--- a/applications/pilot_study/positive/pos_lipid_reference_set.xlsx
+++ b/applications/pilot_study/positive/pos_lipid_reference_set.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saralondonoosorio/Documents/GitHub/CEMBIO-EURAC/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saralondonoosorio/Documents/GitHub/CEMBIO-EURAC/applications/pilot_study/positive/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AF8CB13-C17B-A245-874D-6D121508AE44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5B403EE-20A9-7348-AF0F-981535DA48DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1760" yWindow="760" windowWidth="21360" windowHeight="16780" xr2:uid="{9E5E902E-872A-BE45-A1A9-54571E2C3B45}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="43">
   <si>
     <t>Endogenos</t>
   </si>
@@ -150,6 +150,21 @@
   </si>
   <si>
     <t>TG1</t>
+  </si>
+  <si>
+    <t>Cer(d40:2)</t>
+  </si>
+  <si>
+    <t>Cer</t>
+  </si>
+  <si>
+    <t>ISTD</t>
+  </si>
+  <si>
+    <t>C17 Sphinganine</t>
+  </si>
+  <si>
+    <t>Sphinganine</t>
   </si>
 </sst>
 </file>
@@ -159,7 +174,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -190,6 +205,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -211,7 +232,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -233,6 +254,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -567,7 +589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BFD69E1-DE54-004B-BA8F-573A6CD4FC04}">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="30.6640625" bestFit="1" customWidth="1"/>
@@ -1005,6 +1027,46 @@
         <v>37</v>
       </c>
     </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A20" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="11">
+        <v>678.65070000000003</v>
+      </c>
+      <c r="D20" s="11">
+        <v>12</v>
+      </c>
+      <c r="E20" s="11">
+        <v>720</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A21" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="11">
+        <v>288.28969999999998</v>
+      </c>
+      <c r="D21" s="11">
+        <v>1.99</v>
+      </c>
+      <c r="E21" s="11">
+        <v>119.4</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/applications/pilot_study/positive/pos_lipid_reference_set.xlsx
+++ b/applications/pilot_study/positive/pos_lipid_reference_set.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saralondonoosorio/Documents/GitHub/CEMBIO-EURAC/applications/pilot_study/positive/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5B403EE-20A9-7348-AF0F-981535DA48DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CBEF1C3-CF09-4B48-8A68-02DB6F5490D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1760" yWindow="760" windowWidth="21360" windowHeight="16780" xr2:uid="{9E5E902E-872A-BE45-A1A9-54571E2C3B45}"/>
+    <workbookView xWindow="3220" yWindow="660" windowWidth="26180" windowHeight="17400" xr2:uid="{9E5E902E-872A-BE45-A1A9-54571E2C3B45}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="49">
   <si>
     <t>Endogenos</t>
   </si>
@@ -165,6 +165,24 @@
   </si>
   <si>
     <t>Sphinganine</t>
+  </si>
+  <si>
+    <t>TG(54:4)</t>
+  </si>
+  <si>
+    <t>LPC(0:0/16:0)</t>
+  </si>
+  <si>
+    <t>SM(d18:2/16:0)</t>
+  </si>
+  <si>
+    <t>PC(16:0/18:2)</t>
+  </si>
+  <si>
+    <t>SM(d18:1/20:0)</t>
+  </si>
+  <si>
+    <t>HexCer(d18:1/24:0)</t>
   </si>
 </sst>
 </file>
@@ -643,7 +661,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="C3" s="5">
         <v>496.33980000000003</v>
@@ -735,7 +753,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="C7" s="5">
         <v>701.55920000000003</v>
@@ -804,7 +822,7 @@
         <v>0</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="C10" s="5">
         <v>758.56939999999997</v>
@@ -873,7 +891,7 @@
         <v>0</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="C13" s="8">
         <v>759.63879999999995</v>
@@ -919,7 +937,7 @@
         <v>0</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="C15" s="5">
         <v>812.69740000000002</v>
@@ -942,7 +960,7 @@
         <v>0</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="C16" s="5">
         <v>900.80150000000003</v>

--- a/applications/pilot_study/positive/pos_lipid_reference_set.xlsx
+++ b/applications/pilot_study/positive/pos_lipid_reference_set.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saralondonoosorio/Documents/GitHub/CEMBIO-EURAC/applications/pilot_study/positive/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CBEF1C3-CF09-4B48-8A68-02DB6F5490D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65ED97DA-8F68-4348-A226-B4792989AA95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3220" yWindow="660" windowWidth="26180" windowHeight="17400" xr2:uid="{9E5E902E-872A-BE45-A1A9-54571E2C3B45}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="14720" windowHeight="17400" xr2:uid="{9E5E902E-872A-BE45-A1A9-54571E2C3B45}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -38,57 +38,24 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="49">
   <si>
-    <t>Endogenos</t>
-  </si>
-  <si>
     <t>CAR (5:0)</t>
   </si>
   <si>
-    <t>LysoPC</t>
-  </si>
-  <si>
-    <t>deuterated-LysoPC (18:1(d7))</t>
-  </si>
-  <si>
-    <t>deuterated-LysoPE (18:1(d7))</t>
-  </si>
-  <si>
     <t>LPC (20:0)</t>
   </si>
   <si>
     <t>SM</t>
   </si>
   <si>
-    <t>deuterated-PG (15:0/18:1(d7))</t>
-  </si>
-  <si>
-    <t>deuterated-SM (d18:1/18:1(d9))</t>
-  </si>
-  <si>
     <t>PC</t>
   </si>
   <si>
-    <t>deuterated-PC (15:0/18:1(d7))</t>
-  </si>
-  <si>
-    <t>deuterated-PE (15:0/18:1(d7))</t>
-  </si>
-  <si>
-    <t>deuterated-DG (15:0/18:1(d7))</t>
-  </si>
-  <si>
     <t>HexCer</t>
   </si>
   <si>
     <t>TG</t>
   </si>
   <si>
-    <t>deuterated-TAG (15:0/18:1(d7))/15:0)</t>
-  </si>
-  <si>
-    <t>deuterated-Chol Ester (18:1(d7))</t>
-  </si>
-  <si>
     <t>type</t>
   </si>
   <si>
@@ -107,18 +74,9 @@
     <t>mz</t>
   </si>
   <si>
-    <t>SM1</t>
-  </si>
-  <si>
     <t>CAR</t>
   </si>
   <si>
-    <t>dLysoPC</t>
-  </si>
-  <si>
-    <t>dLysoPE</t>
-  </si>
-  <si>
     <t>LPC</t>
   </si>
   <si>
@@ -149,9 +107,6 @@
     <t>TG(52:0)</t>
   </si>
   <si>
-    <t>TG1</t>
-  </si>
-  <si>
     <t>Cer(d40:2)</t>
   </si>
   <si>
@@ -183,6 +138,51 @@
   </si>
   <si>
     <t>HexCer(d18:1/24:0)</t>
+  </si>
+  <si>
+    <t>LysoPC (18:1(d7))</t>
+  </si>
+  <si>
+    <t>LysoPE (18:1(d7))</t>
+  </si>
+  <si>
+    <t>PG (15:0/18:1(d7))</t>
+  </si>
+  <si>
+    <t>SM (d18:1/18:1(d9))</t>
+  </si>
+  <si>
+    <t>PC (15:0/18:1(d7))</t>
+  </si>
+  <si>
+    <t>PE (15:0/18:1(d7))</t>
+  </si>
+  <si>
+    <t>DG (15:0/18:1(d7))</t>
+  </si>
+  <si>
+    <t>TG(15:0/18:1(d7))/15:0)</t>
+  </si>
+  <si>
+    <t>Chol Ester (18:1(d7))</t>
+  </si>
+  <si>
+    <t>Endogenous</t>
+  </si>
+  <si>
+    <t>SM_1</t>
+  </si>
+  <si>
+    <t>dLPC</t>
+  </si>
+  <si>
+    <t>dLPE</t>
+  </si>
+  <si>
+    <t>TG_1</t>
+  </si>
+  <si>
+    <t>LPC_1</t>
   </si>
 </sst>
 </file>
@@ -192,7 +192,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -205,27 +205,17 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="9"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="9"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
+      <color theme="9" tint="-0.499984740745262"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
@@ -250,34 +240,55 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -608,484 +619,490 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BFD69E1-DE54-004B-BA8F-573A6CD4FC04}">
   <dimension ref="A1:I21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" style="3"/>
+    <col min="2" max="2" width="30.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="10.83203125" style="9"/>
+    <col min="7" max="16384" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>17</v>
+      <c r="A1" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>7</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>11</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" t="s">
-        <v>35</v>
+        <v>8</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="5">
+      <c r="C2" s="8">
         <v>246.17</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="4">
         <v>0.8</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="9">
         <f>D2*60</f>
         <v>48</v>
       </c>
-      <c r="F2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
+      <c r="F2" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" s="5">
+        <v>43</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="8">
         <v>496.33980000000003</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="6">
         <v>2.56</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="9">
         <f t="shared" ref="E3:E18" si="0">D3*60</f>
         <v>153.6</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="8">
+        <v>552.40239999999994</v>
+      </c>
+      <c r="D4" s="6">
+        <v>4.24</v>
+      </c>
+      <c r="E4" s="9">
+        <f>D4*60</f>
+        <v>254.4</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="8">
+        <v>701.55920000000003</v>
+      </c>
+      <c r="D5" s="6">
+        <v>6.19</v>
+      </c>
+      <c r="E5" s="9">
+        <f>D5*60</f>
+        <v>371.40000000000003</v>
+      </c>
+      <c r="F5" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="8">
+        <v>758.56939999999997</v>
+      </c>
+      <c r="D6" s="6">
+        <v>7.76</v>
+      </c>
+      <c r="E6" s="9">
+        <f>D6*60</f>
+        <v>465.59999999999997</v>
+      </c>
+      <c r="F6" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="8">
-        <v>529.39940000000001</v>
-      </c>
-      <c r="D4" s="9">
-        <v>2.7429999999999999</v>
-      </c>
-      <c r="E4">
-        <f t="shared" si="0"/>
-        <v>164.57999999999998</v>
-      </c>
-      <c r="F4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="8">
+        <v>759.63879999999995</v>
+      </c>
+      <c r="D7" s="4">
+        <v>11.43</v>
+      </c>
+      <c r="E7" s="9">
+        <f>D7*60</f>
+        <v>685.8</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="8">
+        <v>812.69740000000002</v>
+      </c>
+      <c r="D8" s="6">
+        <v>12.25</v>
+      </c>
+      <c r="E8" s="9">
+        <f>D8*60</f>
+        <v>735</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="8">
-        <v>487.35239999999999</v>
-      </c>
-      <c r="D5" s="9">
-        <v>2.8479999999999999</v>
-      </c>
-      <c r="E5">
-        <f t="shared" si="0"/>
-        <v>170.88</v>
-      </c>
-      <c r="F5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="8">
+        <v>900.80150000000003</v>
+      </c>
+      <c r="D9" s="6">
+        <v>13.97</v>
+      </c>
+      <c r="E9" s="9">
+        <f>D9*60</f>
+        <v>838.2</v>
+      </c>
+      <c r="F9" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="5">
-        <v>552.40239999999994</v>
-      </c>
-      <c r="D6" s="7">
-        <v>4.24</v>
-      </c>
-      <c r="E6">
-        <f t="shared" si="0"/>
-        <v>254.4</v>
-      </c>
-      <c r="F6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C7" s="5">
-        <v>701.55920000000003</v>
-      </c>
-      <c r="D7" s="7">
-        <v>6.19</v>
-      </c>
-      <c r="E7">
-        <f t="shared" si="0"/>
-        <v>371.40000000000003</v>
-      </c>
-      <c r="F7" t="s">
-        <v>6</v>
-      </c>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="8">
-        <v>759.58749999999998</v>
-      </c>
-      <c r="D8" s="9">
-        <v>6.46</v>
-      </c>
-      <c r="E8">
-        <f t="shared" si="0"/>
-        <v>387.6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="8">
-        <v>738.64700000000005</v>
-      </c>
-      <c r="D9" s="9">
-        <v>7.2709999999999999</v>
-      </c>
-      <c r="E9">
-        <f t="shared" si="0"/>
-        <v>436.26</v>
-      </c>
-      <c r="F9" t="s">
-        <v>29</v>
-      </c>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="5">
-        <v>758.56939999999997</v>
-      </c>
-      <c r="D10" s="7">
-        <v>7.76</v>
-      </c>
-      <c r="E10">
-        <f t="shared" si="0"/>
-        <v>465.59999999999997</v>
-      </c>
-      <c r="F10" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
+        <v>43</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="8">
+        <v>880.83274340259902</v>
+      </c>
+      <c r="D10" s="6">
+        <v>16.05</v>
+      </c>
+      <c r="E10" s="9">
+        <f>D10*60</f>
+        <v>963</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="1" t="s">
+      <c r="A11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="9">
+        <v>678.65070000000003</v>
+      </c>
+      <c r="D11" s="9">
+        <v>12</v>
+      </c>
+      <c r="E11" s="9">
+        <v>720</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="8">
+      <c r="B12" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="11">
+        <v>759.58749999999998</v>
+      </c>
+      <c r="D12" s="12">
+        <v>6.46</v>
+      </c>
+      <c r="E12" s="13">
+        <f>D12*60</f>
+        <v>387.6</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="11">
+        <v>738.64700000000005</v>
+      </c>
+      <c r="D13" s="12">
+        <v>7.2709999999999999</v>
+      </c>
+      <c r="E13" s="13">
+        <f>D13*60</f>
+        <v>436.26</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="11">
         <v>753.61339999999996</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D14" s="12">
         <v>8.1709999999999994</v>
       </c>
-      <c r="E11">
-        <f t="shared" si="0"/>
+      <c r="E14" s="13">
+        <f>D14*60</f>
         <v>490.26</v>
       </c>
-      <c r="F11" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="8">
+      <c r="F14" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="11">
         <v>711.56640000000004</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D15" s="12">
         <v>8.5030000000000001</v>
       </c>
-      <c r="E12">
-        <f t="shared" si="0"/>
+      <c r="E15" s="13">
+        <f>D15*60</f>
         <v>510.18</v>
       </c>
-      <c r="F12" t="s">
-        <v>31</v>
-      </c>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" s="8">
-        <v>759.63879999999995</v>
-      </c>
-      <c r="D13" s="10">
-        <v>11.43</v>
-      </c>
-      <c r="E13">
-        <f t="shared" si="0"/>
-        <v>685.8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>23</v>
-      </c>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="8">
+      <c r="F15" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="11">
         <v>605.58439999999996</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D16" s="12">
         <v>11.68</v>
       </c>
-      <c r="E14">
-        <f t="shared" si="0"/>
+      <c r="E16" s="13">
+        <f>D16*60</f>
         <v>700.8</v>
       </c>
-      <c r="F14" t="s">
-        <v>32</v>
-      </c>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" s="5">
-        <v>812.69740000000002</v>
-      </c>
-      <c r="D15" s="7">
-        <v>12.25</v>
-      </c>
-      <c r="E15">
-        <f t="shared" si="0"/>
-        <v>735</v>
-      </c>
-      <c r="F15" t="s">
-        <v>13</v>
-      </c>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" s="5">
-        <v>900.80150000000003</v>
-      </c>
-      <c r="D16" s="7">
-        <v>13.97</v>
-      </c>
-      <c r="E16">
-        <f t="shared" si="0"/>
-        <v>838.2</v>
-      </c>
-      <c r="F16" t="s">
-        <v>14</v>
-      </c>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
+      <c r="F16" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="8">
+      <c r="A17" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="11">
         <v>829.79849999999999</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="12">
         <v>13.997999999999999</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="13">
         <f t="shared" si="0"/>
         <v>839.88</v>
       </c>
-      <c r="F17" t="s">
-        <v>33</v>
-      </c>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
+      <c r="F17" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="8">
+      <c r="A18" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="11">
         <v>675.67790000000002</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="12">
         <v>15.46</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="13">
         <f t="shared" si="0"/>
         <v>927.6</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>0</v>
-      </c>
-      <c r="B19" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" s="8">
-        <v>880.83274340259902</v>
-      </c>
-      <c r="D19" s="9">
-        <v>16.05</v>
-      </c>
-      <c r="E19">
+      <c r="C19" s="11">
+        <v>529.39940000000001</v>
+      </c>
+      <c r="D19" s="12">
+        <v>2.7429999999999999</v>
+      </c>
+      <c r="E19" s="13">
         <f>D19*60</f>
-        <v>963</v>
-      </c>
-      <c r="F19" t="s">
-        <v>37</v>
+        <v>164.57999999999998</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A20" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>38</v>
+      <c r="A20" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="C20" s="11">
-        <v>678.65070000000003</v>
-      </c>
-      <c r="D20" s="11">
-        <v>12</v>
-      </c>
-      <c r="E20" s="11">
-        <v>720</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>39</v>
+        <v>487.35239999999999</v>
+      </c>
+      <c r="D20" s="12">
+        <v>2.8479999999999999</v>
+      </c>
+      <c r="E20" s="13">
+        <f>D20*60</f>
+        <v>170.88</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A21" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" s="11">
+      <c r="A21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="9">
         <v>288.28969999999998</v>
       </c>
-      <c r="D21" s="11">
+      <c r="D21" s="9">
         <v>1.99</v>
       </c>
-      <c r="E21" s="11">
+      <c r="E21" s="9">
         <v>119.4</v>
       </c>
-      <c r="F21" s="11" t="s">
-        <v>42</v>
+      <c r="F21" s="9" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="F1:F1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>